--- a/CAPSTONE/M01/bus123-capstone-m01-l01-starter.xlsx
+++ b/CAPSTONE/M01/bus123-capstone-m01-l01-starter.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rab99cdf7dfb24542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Re11d5b420da14b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R2b76f6e537934c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Ra02a877c741d4995"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -442,19 +442,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="71.11000061035156" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="25.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65.55999755859375" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14.4399995803833" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="29" t="str">
-        <x:v>Northstar Bike Studio Finance Capstone</x:v>
+        <x:v>Northstar Athletic Studio Finance Capstone</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str"/>
       <x:c r="C1" s="29" t="str"/>
@@ -474,7 +474,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="31" t="str">
-        <x:v>This starter workbook gives you only the project overview and case assumptions. You build the model.</x:v>
+        <x:v>This starter workbook gives you the case assumptions and process checklist. You build the model.</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str"/>
       <x:c r="C2" s="31" t="str"/>
@@ -515,7 +515,7 @@
         <x:v>Project question</x:v>
       </x:c>
       <x:c r="B4" s="26" t="str">
-        <x:v>Which financing option gives Northstar Bike Studio the best chance of surviving its first year?</x:v>
+        <x:v>Which financing option gives Northstar Athletic Studio the best chance of surviving its first year?</x:v>
       </x:c>
       <x:c r="C4" s="30"/>
       <x:c r="D4" s="32" t="str">
@@ -543,7 +543,7 @@
         <x:v>Your job</x:v>
       </x:c>
       <x:c r="B5" s="26" t="str">
-        <x:v>Create the model tabs, add the rows and columns, format the workbook, write formulas, create charts, and make a recommendation.</x:v>
+        <x:v>Create the model tabs, add rows and columns, format the workbook, write formulas, create charts, document your process, and make a recommendation.</x:v>
       </x:c>
       <x:c r="C5" s="30"/>
       <x:c r="D5" s="27" t="str">
@@ -567,7 +567,7 @@
         <x:v>Use this workbook for</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>Project directions, submission checklist, and business assumptions.</x:v>
+        <x:v>Project directions, submission checklist, process evidence checklist, and business assumptions.</x:v>
       </x:c>
       <x:c r="C6" s="30"/>
       <x:c r="D6" s="27" t="str">
@@ -612,10 +612,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="32" t="str">
-        <x:v>Required tab 1</x:v>
+        <x:v>Explainability standard</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>Startup Budget</x:v>
+        <x:v>You must be able to explain every formula, formatting choice, chart, and recommendation in your submitted workbook.</x:v>
       </x:c>
       <x:c r="C8" s="30"/>
       <x:c r="D8" s="27" t="str">
@@ -636,10 +636,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="32" t="str">
-        <x:v>Required tab 2</x:v>
+        <x:v>Required tab 1</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>Financing Model</x:v>
+        <x:v>Startup Budget</x:v>
       </x:c>
       <x:c r="C9" s="30"/>
       <x:c r="D9" s="27" t="str">
@@ -660,10 +660,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="32" t="str">
-        <x:v>Required tab 3</x:v>
+        <x:v>Required tab 2</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>Revenue Forecast</x:v>
+        <x:v>Financing Model</x:v>
       </x:c>
       <x:c r="C10" s="30"/>
       <x:c r="D10" s="27" t="str">
@@ -684,10 +684,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="32" t="str">
-        <x:v>Required tab 4</x:v>
+        <x:v>Required tab 3</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>Cash Flow Model</x:v>
+        <x:v>Revenue Forecast</x:v>
       </x:c>
       <x:c r="C11" s="30"/>
       <x:c r="D11" s="27" t="str">
@@ -708,10 +708,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="32" t="str">
-        <x:v>Required tab 5</x:v>
+        <x:v>Required tab 4</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>Break-Even Analysis</x:v>
+        <x:v>Cash Flow Model</x:v>
       </x:c>
       <x:c r="C12" s="30"/>
       <x:c r="D12" s="27" t="str">
@@ -732,10 +732,10 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="32" t="str">
-        <x:v>Required tab 6</x:v>
+        <x:v>Required tab 5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>Dashboard</x:v>
+        <x:v>Break-Even Analysis</x:v>
       </x:c>
       <x:c r="C13" s="30"/>
       <x:c r="D13" s="27" t="str">
@@ -756,10 +756,10 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="32" t="str">
-        <x:v>Required tab 7</x:v>
+        <x:v>Required tab 6</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>Recommendation</x:v>
+        <x:v>Dashboard</x:v>
       </x:c>
       <x:c r="C14" s="30"/>
       <x:c r="D14" s="27" t="str">
@@ -779,12 +779,18 @@
       <x:c r="P14" s="30"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="30"/>
-      <x:c r="B15" s="30"/>
+      <x:c r="A15" s="32" t="str">
+        <x:v>Required tab 7</x:v>
+      </x:c>
+      <x:c r="B15" s="26" t="str">
+        <x:v>Recommendation or Build Log</x:v>
+      </x:c>
       <x:c r="C15" s="30"/>
-      <x:c r="D15" s="30"/>
-      <x:c r="E15" s="30"/>
-      <x:c r="F15" s="30"/>
+      <x:c r="D15" s="27" t="str">
+        <x:v>Completed process evidence</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="str"/>
+      <x:c r="F15" s="26" t="str"/>
       <x:c r="G15" s="30"/>
       <x:c r="H15" s="30"/>
       <x:c r="I15" s="30"/>
@@ -833,12 +839,22 @@
       <x:c r="P17" s="30"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="30"/>
-      <x:c r="B18" s="30"/>
-      <x:c r="C18" s="30"/>
-      <x:c r="D18" s="30"/>
-      <x:c r="E18" s="30"/>
-      <x:c r="F18" s="30"/>
+      <x:c r="A18" s="32" t="str">
+        <x:v>Process Evidence</x:v>
+      </x:c>
+      <x:c r="B18" s="32" t="str">
+        <x:v>What to include</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="str"/>
+      <x:c r="D18" s="32" t="str">
+        <x:v>Defense Prompts</x:v>
+      </x:c>
+      <x:c r="E18" s="32" t="str">
+        <x:v>Prepared?</x:v>
+      </x:c>
+      <x:c r="F18" s="32" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
       <x:c r="G18" s="30"/>
       <x:c r="H18" s="30"/>
       <x:c r="I18" s="30"/>
@@ -851,12 +867,18 @@
       <x:c r="P18" s="30"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="30"/>
-      <x:c r="B19" s="30"/>
-      <x:c r="C19" s="30"/>
-      <x:c r="D19" s="30"/>
-      <x:c r="E19" s="30"/>
-      <x:c r="F19" s="30"/>
+      <x:c r="A19" s="27" t="str">
+        <x:v>Build log</x:v>
+      </x:c>
+      <x:c r="B19" s="26" t="str">
+        <x:v>5-8 bullets explaining how you built the workbook</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="str"/>
+      <x:c r="D19" s="26" t="str">
+        <x:v>Walk me through your cash flow model.</x:v>
+      </x:c>
+      <x:c r="E19" s="28" t="str"/>
+      <x:c r="F19" s="26" t="str"/>
       <x:c r="G19" s="30"/>
       <x:c r="H19" s="30"/>
       <x:c r="I19" s="30"/>
@@ -869,12 +891,18 @@
       <x:c r="P19" s="30"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="30"/>
-      <x:c r="B20" s="30"/>
-      <x:c r="C20" s="30"/>
-      <x:c r="D20" s="30"/>
-      <x:c r="E20" s="30"/>
-      <x:c r="F20" s="30"/>
+      <x:c r="A20" s="27" t="str">
+        <x:v>Formula explanation 1</x:v>
+      </x:c>
+      <x:c r="B20" s="26" t="str">
+        <x:v>Bank loan monthly payment formula</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="str"/>
+      <x:c r="D20" s="26" t="str">
+        <x:v>Explain how your bank PMT formula works.</x:v>
+      </x:c>
+      <x:c r="E20" s="28" t="str"/>
+      <x:c r="F20" s="26" t="str"/>
       <x:c r="G20" s="30"/>
       <x:c r="H20" s="30"/>
       <x:c r="I20" s="30"/>
@@ -887,12 +915,18 @@
       <x:c r="P20" s="30"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="30"/>
-      <x:c r="B21" s="30"/>
-      <x:c r="C21" s="30"/>
-      <x:c r="D21" s="30"/>
-      <x:c r="E21" s="30"/>
-      <x:c r="F21" s="30"/>
+      <x:c r="A21" s="27" t="str">
+        <x:v>Formula explanation 2</x:v>
+      </x:c>
+      <x:c r="B21" s="26" t="str">
+        <x:v>Equipment financing monthly payment formula</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="str"/>
+      <x:c r="D21" s="26" t="str">
+        <x:v>Explain how equipment financing differs from the bank loan.</x:v>
+      </x:c>
+      <x:c r="E21" s="28" t="str"/>
+      <x:c r="F21" s="26" t="str"/>
       <x:c r="G21" s="30"/>
       <x:c r="H21" s="30"/>
       <x:c r="I21" s="30"/>
@@ -905,12 +939,18 @@
       <x:c r="P21" s="30"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="30"/>
-      <x:c r="B22" s="30"/>
-      <x:c r="C22" s="30"/>
-      <x:c r="D22" s="30"/>
-      <x:c r="E22" s="30"/>
-      <x:c r="F22" s="30"/>
+      <x:c r="A22" s="27" t="str">
+        <x:v>Formula explanation 3</x:v>
+      </x:c>
+      <x:c r="B22" s="26" t="str">
+        <x:v>Investor payment formula</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="str"/>
+      <x:c r="D22" s="26" t="str">
+        <x:v>Why can the investor payment not go below zero?</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="str"/>
+      <x:c r="F22" s="26" t="str"/>
       <x:c r="G22" s="30"/>
       <x:c r="H22" s="30"/>
       <x:c r="I22" s="30"/>
@@ -923,12 +963,18 @@
       <x:c r="P22" s="30"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="30"/>
-      <x:c r="B23" s="30"/>
-      <x:c r="C23" s="30"/>
-      <x:c r="D23" s="30"/>
-      <x:c r="E23" s="30"/>
-      <x:c r="F23" s="30"/>
+      <x:c r="A23" s="27" t="str">
+        <x:v>Formula explanation 4</x:v>
+      </x:c>
+      <x:c r="B23" s="26" t="str">
+        <x:v>Break-even members formula</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="str"/>
+      <x:c r="D23" s="26" t="str">
+        <x:v>What costs are included in break-even members?</x:v>
+      </x:c>
+      <x:c r="E23" s="28" t="str"/>
+      <x:c r="F23" s="26" t="str"/>
       <x:c r="G23" s="30"/>
       <x:c r="H23" s="30"/>
       <x:c r="I23" s="30"/>
@@ -941,12 +987,18 @@
       <x:c r="P23" s="30"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="30"/>
-      <x:c r="B24" s="30"/>
-      <x:c r="C24" s="30"/>
-      <x:c r="D24" s="30"/>
-      <x:c r="E24" s="30"/>
-      <x:c r="F24" s="30"/>
+      <x:c r="A24" s="27" t="str">
+        <x:v>In-class checkpoint</x:v>
+      </x:c>
+      <x:c r="B24" s="26" t="str">
+        <x:v>Show one partially built model section during class</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="str"/>
+      <x:c r="D24" s="26" t="str">
+        <x:v>Which section did you build first and why?</x:v>
+      </x:c>
+      <x:c r="E24" s="28" t="str"/>
+      <x:c r="F24" s="26" t="str"/>
       <x:c r="G24" s="30"/>
       <x:c r="H24" s="30"/>
       <x:c r="I24" s="30"/>
@@ -959,12 +1011,18 @@
       <x:c r="P24" s="30"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="30"/>
-      <x:c r="B25" s="30"/>
-      <x:c r="C25" s="30"/>
-      <x:c r="D25" s="30"/>
-      <x:c r="E25" s="30"/>
-      <x:c r="F25" s="30"/>
+      <x:c r="A25" s="27" t="str">
+        <x:v>Version evidence</x:v>
+      </x:c>
+      <x:c r="B25" s="26" t="str">
+        <x:v>Keep OneDrive/Excel version history available if requested</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="str"/>
+      <x:c r="D25" s="26" t="str">
+        <x:v>What changed between your early draft and final workbook?</x:v>
+      </x:c>
+      <x:c r="E25" s="28" t="str"/>
+      <x:c r="F25" s="26" t="str"/>
       <x:c r="G25" s="30"/>
       <x:c r="H25" s="30"/>
       <x:c r="I25" s="30"/>
@@ -977,12 +1035,18 @@
       <x:c r="P25" s="30"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="30"/>
-      <x:c r="B26" s="30"/>
-      <x:c r="C26" s="30"/>
-      <x:c r="D26" s="30"/>
-      <x:c r="E26" s="30"/>
-      <x:c r="F26" s="30"/>
+      <x:c r="A26" s="27" t="str">
+        <x:v>Individual variation</x:v>
+      </x:c>
+      <x:c r="B26" s="26" t="str">
+        <x:v>Update the model if your instructor changes one assumption</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="str"/>
+      <x:c r="D26" s="26" t="str">
+        <x:v>What would change if expected members were 10% lower?</x:v>
+      </x:c>
+      <x:c r="E26" s="28" t="str"/>
+      <x:c r="F26" s="26" t="str"/>
       <x:c r="G26" s="30"/>
       <x:c r="H26" s="30"/>
       <x:c r="I26" s="30"/>
@@ -995,12 +1059,18 @@
       <x:c r="P26" s="30"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="30"/>
-      <x:c r="B27" s="30"/>
-      <x:c r="C27" s="30"/>
-      <x:c r="D27" s="30"/>
-      <x:c r="E27" s="30"/>
-      <x:c r="F27" s="30"/>
+      <x:c r="A27" s="27" t="str">
+        <x:v>Formatting defense</x:v>
+      </x:c>
+      <x:c r="B27" s="26" t="str">
+        <x:v>Identify one formatting choice that improved readability</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="str"/>
+      <x:c r="D27" s="26" t="str">
+        <x:v>Which formatting choice would help a manager most?</x:v>
+      </x:c>
+      <x:c r="E27" s="28" t="str"/>
+      <x:c r="F27" s="26" t="str"/>
       <x:c r="G27" s="30"/>
       <x:c r="H27" s="30"/>
       <x:c r="I27" s="30"/>
@@ -1013,12 +1083,18 @@
       <x:c r="P27" s="30"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="30"/>
-      <x:c r="B28" s="30"/>
-      <x:c r="C28" s="30"/>
-      <x:c r="D28" s="30"/>
-      <x:c r="E28" s="30"/>
-      <x:c r="F28" s="30"/>
+      <x:c r="A28" s="27" t="str">
+        <x:v>Recommendation defense</x:v>
+      </x:c>
+      <x:c r="B28" s="26" t="str">
+        <x:v>Use model metrics to defend your final recommendation</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="str"/>
+      <x:c r="D28" s="26" t="str">
+        <x:v>Why did you recommend this financing option?</x:v>
+      </x:c>
+      <x:c r="E28" s="28" t="str"/>
+      <x:c r="F28" s="26" t="str"/>
       <x:c r="G28" s="30"/>
       <x:c r="H28" s="30"/>
       <x:c r="I28" s="30"/>
@@ -1284,14 +1360,14 @@
       <x:c r="F1" s="29" t="str"/>
       <x:c r="G1" s="29" t="str"/>
       <x:c r="H1" s="29" t="str"/>
-      <x:c r="I1" s="30"/>
-      <x:c r="J1" s="30"/>
-      <x:c r="K1" s="30"/>
-      <x:c r="L1" s="30"/>
-      <x:c r="M1" s="30"/>
-      <x:c r="N1" s="30"/>
-      <x:c r="O1" s="30"/>
-      <x:c r="P1" s="30"/>
+      <x:c r="I1" s="29" t="str"/>
+      <x:c r="J1" s="29" t="str"/>
+      <x:c r="K1" s="29" t="str"/>
+      <x:c r="L1" s="29" t="str"/>
+      <x:c r="M1" s="29" t="str"/>
+      <x:c r="N1" s="29" t="str"/>
+      <x:c r="O1" s="29" t="str"/>
+      <x:c r="P1" s="29" t="str"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="31" t="str">
@@ -1304,14 +1380,14 @@
       <x:c r="F2" s="31" t="str"/>
       <x:c r="G2" s="31" t="str"/>
       <x:c r="H2" s="31" t="str"/>
-      <x:c r="I2" s="30"/>
-      <x:c r="J2" s="30"/>
-      <x:c r="K2" s="30"/>
-      <x:c r="L2" s="30"/>
-      <x:c r="M2" s="30"/>
-      <x:c r="N2" s="30"/>
-      <x:c r="O2" s="30"/>
-      <x:c r="P2" s="30"/>
+      <x:c r="I2" s="31" t="str"/>
+      <x:c r="J2" s="31" t="str"/>
+      <x:c r="K2" s="31" t="str"/>
+      <x:c r="L2" s="31" t="str"/>
+      <x:c r="M2" s="31" t="str"/>
+      <x:c r="N2" s="31" t="str"/>
+      <x:c r="O2" s="31" t="str"/>
+      <x:c r="P2" s="31" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="30"/>

--- a/CAPSTONE/M01/bus123-capstone-m01-l01-starter.xlsx
+++ b/CAPSTONE/M01/bus123-capstone-m01-l01-starter.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R2b76f6e537934c73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Ra02a877c741d4995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rfd88f6b363be4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R895858418f104b05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="202" formatCode="0"/>
     <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);-"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -91,6 +91,11 @@
       <x:color rgb="FF1F4E79"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
   <x:fills count="6">
     <x:fill>
@@ -140,7 +145,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -238,6 +243,12 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -290,9 +301,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1680,10 +1691,10 @@
       <x:c r="B14" s="30"/>
       <x:c r="C14" s="30"/>
       <x:c r="D14" s="27" t="str">
-        <x:v>Private event revenue per month</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="n">
-        <x:v>600</x:v>
+        <x:v>Drop-in visits per month</x:v>
+      </x:c>
+      <x:c r="E14" s="39" t="n">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F14" s="30"/>
       <x:c r="G14" s="30"/>
@@ -1701,8 +1712,12 @@
       <x:c r="A15" s="30"/>
       <x:c r="B15" s="30"/>
       <x:c r="C15" s="30"/>
-      <x:c r="D15" s="30"/>
-      <x:c r="E15" s="30"/>
+      <x:c r="D15" s="30" t="str">
+        <x:v>Private event revenue per month</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="n">
+        <x:v>600</x:v>
+      </x:c>
       <x:c r="F15" s="30"/>
       <x:c r="G15" s="30"/>
       <x:c r="H15" s="30"/>
